--- a/tests/Testing_Document.xlsx
+++ b/tests/Testing_Document.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\System_Design\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B1D686-6774-404B-99E6-D45105462757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76E3E71-9A58-4E81-BBB4-4A64CAFF8DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2491,7 +2491,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.625" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="2" max="2" width="39.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39" customWidth="1"/>
     <col min="4" max="4" width="29.375" customWidth="1"/>
     <col min="5" max="5" width="114" bestFit="1" customWidth="1"/>

--- a/tests/Testing_Document.xlsx
+++ b/tests/Testing_Document.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>File CSV được tải xuống thành công, hiển thị đầy đủ nội dung bằng tiếng Việt.</t>
+          <t>Tải xuống file PDF báo cáo doanh thu thành công từ backend, Content-Type chuẩn application/pdf.</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>VietQR động được tạo chính xác với số tiền hóa đơn thật và nội dung chuyển khoản tự động.</t>
+          <t>Sinh link thanh toán VNPay thành công cho hoá đơn 6a186ee7a54f4b96cd635f08: https://sandbox.vnpayment.vn/paymentv2/vpcpay.html?vnp_Amoun...</t>
         </is>
       </c>
       <c r="G95" s="9" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>Giao diện hiển thị nút thanh toán ở trạng thái disabled và hiển thị badge Đã thanh toán.</t>
+          <t>Hoá đơn 6a186ee7a54f4b96cd635f17 đã thanh toán, hiển thị trạng thái 'paid'.</t>
         </is>
       </c>
       <c r="G96" s="9" t="inlineStr">

--- a/tests/Testing_Document.xlsx
+++ b/tests/Testing_Document.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Arial"/>
       <family val="2"/>
@@ -65,8 +65,20 @@
       <color rgb="00006100"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C6500"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +101,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -147,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -170,6 +194,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2191,9 +2221,9 @@
           <t>Trang chi tiết hiển thị đầy đủ số liệu thống kê phòng và phân công quản lý.</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2229,9 +2259,9 @@
           <t>DB cập nhật tên cơ sở mới thành công, giao diện cập nhật tức thời.</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2267,9 +2297,9 @@
           <t>Bảng danh sách hiển thị đầy đủ tài khoản người dùng kèm vai trò cụ thể.</t>
         </is>
       </c>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2305,9 +2335,9 @@
           <t>Indicator pill trượt mượt sang tab mới và danh sách tự lọc theo vai trò.</t>
         </is>
       </c>
-      <c r="G45" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2343,9 +2373,9 @@
           <t>Hệ thống lọc danh sách người dùng theo tên khớp thời gian thực.</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2384,9 +2414,9 @@
           <t>Thêm tài khoản thành công, mật khẩu mặc định được mã hóa băm bcrypt.</t>
         </is>
       </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2422,9 +2452,9 @@
           <t>Hệ thống cập nhật thông tin thành công, hiển thị thông báo kết quả.</t>
         </is>
       </c>
-      <c r="G48" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2460,9 +2490,9 @@
           <t>Tài khoản đổi trạng thái sang locked thành công trong DB và chặn đăng nhập.</t>
         </is>
       </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2499,9 +2529,9 @@
           <t>Xóa tài khoản khỏi MongoDB thành công, danh sách cập nhật ngay lập tức.</t>
         </is>
       </c>
-      <c r="G50" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2537,9 +2567,9 @@
           <t>Bảng hợp đồng tải dữ liệu thật, hiển thị chi tiết các cột thông tin.</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2575,9 +2605,9 @@
           <t>Hệ thống lọc chính xác các hợp đồng nháp chưa kích hoạt hiệu lực.</t>
         </is>
       </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2613,9 +2643,9 @@
           <t>Modal PDF Viewer hiển thị chính xác nội dung hợp đồng và con dấu ký số điện tử.</t>
         </is>
       </c>
-      <c r="G53" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2651,9 +2681,9 @@
           <t>Tải đầy đủ danh sách hóa đơn từ MongoDB hiển thị trực quan.</t>
         </is>
       </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2689,9 +2719,9 @@
           <t>Hệ thống lọc chính xác các hóa đơn chưa hoàn thành thanh toán.</t>
         </is>
       </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G55" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2727,9 +2757,9 @@
           <t>Bảng kê chi tiết tiền phòng và dịch vụ điện nước hiển thị đầy đủ, chính xác.</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2765,9 +2795,9 @@
           <t>Danh sách công nợ hiển thị thông tin nợ theo từng phòng trọ chính xác.</t>
         </is>
       </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2803,9 +2833,9 @@
           <t>Danh sách các loại dịch vụ kèm cách tính đơn giá hiển thị đầy đủ.</t>
         </is>
       </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2842,9 +2872,9 @@
           <t>Ghi nhận dịch vụ mới thành công vào DB và hiển thị trên màn hình cấu hình.</t>
         </is>
       </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2880,9 +2910,9 @@
           <t>Cập nhật đơn giá mới thành công, áp dụng ngay cho các hóa đơn tạo mới.</t>
         </is>
       </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2918,9 +2948,9 @@
           <t>Biểu đồ Recharts hiển thị chính xác doanh số tổng thu từ DB thật.</t>
         </is>
       </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -2994,9 +3024,9 @@
           <t>Giao diện cài đặt hiển thị đầy đủ cấu hình kết nối email và Telegram Bot API.</t>
         </is>
       </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3032,9 +3062,9 @@
           <t>Cập nhật mật khẩu băm mới thành công, hiển thị Toast thông báo kết quả.</t>
         </is>
       </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3070,9 +3100,9 @@
           <t>Logo hệ thống được cập nhật thành công và đồng bộ trên giao diện.</t>
         </is>
       </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3108,9 +3138,9 @@
           <t>Danh sách thông báo nội bộ hiển thị đầy đủ kèm thời gian phát hành.</t>
         </is>
       </c>
-      <c r="G66" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3146,9 +3176,9 @@
           <t>Badge thông báo được đưa về 0, trạng thái daDoc cập nhật thành công.</t>
         </is>
       </c>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G67" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3184,9 +3214,9 @@
           <t>Giao diện hiển thị đúng số liệu thống kê của các cơ sở được phân công phụ trách.</t>
         </is>
       </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3222,9 +3252,9 @@
           <t>Bảng hiển thị trạng thái các phòng (empty, rented, maintenance, reserved) trực quan.</t>
         </is>
       </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3260,9 +3290,9 @@
           <t>Sơ đồ phòng hiển thị đầy đủ các phòng phân biệt màu trạng thái rõ ràng.</t>
         </is>
       </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3301,9 +3331,9 @@
           <t>Tạo phòng mới thành công, hiển thị ô phòng màu xám trống trên sơ đồ phòng.</t>
         </is>
       </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3340,9 +3370,9 @@
           <t>Cập nhật thông tin phòng thành công, modal đóng lại tự động.</t>
         </is>
       </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G72" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3378,9 +3408,9 @@
           <t>Panel bên phải hiển thị đầy đủ thông tin phòng 101 và mảng tài sản nhúng chi tiết.</t>
         </is>
       </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3416,9 +3446,9 @@
           <t>Sơ đồ phòng tự lọc chỉ hiển thị các phòng trống thỏa mãn điều kiện.</t>
         </is>
       </c>
-      <c r="G74" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G74" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3455,9 +3485,9 @@
           <t>Xóa phòng thành công, sơ đồ phòng cập nhật loại bỏ ô phòng trọ tương ứng.</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3493,9 +3523,9 @@
           <t>Tải dữ liệu danh sách hợp đồng của cơ sở quản lý thành công.</t>
         </is>
       </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G76" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3535,9 +3565,9 @@
           <t>Sinh hợp đồng nháp thành công ở trạng thái draft, gửi yêu cầu ký số đến khách thuê.</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3574,9 +3604,9 @@
           <t>Hệ thống báo lỗi thiếu trường thông tin bắt buộc và chặn chuyển bước.</t>
         </is>
       </c>
-      <c r="G78" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G78" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3612,9 +3642,9 @@
           <t>Modal hiển thị chi tiết thông số hợp đồng và danh mục tài sản nhúng bàn giao phòng.</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3650,9 +3680,9 @@
           <t>Bảng ghi hiển thị chỉ số cũ của các phòng occupied lấy từ MongoDB kỳ trước.</t>
         </is>
       </c>
-      <c r="G80" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G80" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3689,9 +3719,9 @@
           <t>Lưu chỉ số mới thành công, tự động tính điện tiêu thụ = 150 kWh, nước = 10 m3.</t>
         </is>
       </c>
-      <c r="G81" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3727,9 +3757,9 @@
           <t>Hệ thống báo lỗi chỉ số mới không hợp lệ và không cho phép click lưu.</t>
         </is>
       </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G82" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3765,9 +3795,9 @@
           <t>Gửi thông báo tiền dịch vụ thành công qua API Telegram và Nodemailer.</t>
         </is>
       </c>
-      <c r="G83" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3803,9 +3833,9 @@
           <t>Tải danh sách hóa đơn chờ đóng phí của chi nhánh thành công.</t>
         </is>
       </c>
-      <c r="G84" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G84" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3841,9 +3871,9 @@
           <t>Cập nhật trạng thái hóa đơn sang paid trong DB, sinh phiếu thu tiền mặt.</t>
         </is>
       </c>
-      <c r="G85" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3879,9 +3909,9 @@
           <t>Hệ thống hủy phiên thanh toán lỗi, đưa hóa đơn về trạng thái pending.</t>
         </is>
       </c>
-      <c r="G86" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G86" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3917,9 +3947,9 @@
           <t>Hiển thị danh sách thông báo quản lý vận hành cơ sở chi tiết.</t>
         </is>
       </c>
-      <c r="G87" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3955,9 +3985,9 @@
           <t>Giao diện hiển thị đúng thông số phòng thuê, công nợ tháng hiện tại của Tenant.</t>
         </is>
       </c>
-      <c r="G88" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G88" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -3993,9 +4023,9 @@
           <t>Chuyển hướng thành công sang giao diện hóa đơn chờ thanh toán.</t>
         </is>
       </c>
-      <c r="G89" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G89" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4031,9 +4061,9 @@
           <t>Bảng hiển thị hợp đồng cá nhân kèm trạng thái hợp đồng chính xác.</t>
         </is>
       </c>
-      <c r="G90" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G90" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4069,9 +4099,9 @@
           <t>Modal hiển thị đầy đủ văn bản hợp đồng chi tiết và danh mục tài sản bàn giao.</t>
         </is>
       </c>
-      <c r="G91" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G91" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4107,9 +4137,9 @@
           <t>Tải thành công danh sách hóa đơn cá nhân từ database.</t>
         </is>
       </c>
-      <c r="G92" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G92" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4145,9 +4175,9 @@
           <t>Danh sách lọc chính xác các hóa đơn chưa đóng tiền trọ.</t>
         </is>
       </c>
-      <c r="G93" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G93" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4183,9 +4213,9 @@
           <t>Bảng kê chỉ số điện nước tiêu thụ thực tế và đơn giá tương ứng hiển thị đầy đủ.</t>
         </is>
       </c>
-      <c r="G94" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G94" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4298,9 +4328,9 @@
           <t>Trang hồ sơ hiển thị chính xác thông tin liên lạc và checkbox nhận thông báo Telegram.</t>
         </is>
       </c>
-      <c r="G97" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G97" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4337,9 +4367,9 @@
           <t>Hệ thống băm mật khẩu mới cập nhật vào DB thành công, thông báo kết quả.</t>
         </is>
       </c>
-      <c r="G98" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G98" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4376,9 +4406,9 @@
           <t>Hệ thống đối soát mật khẩu cũ thất bại và trả lỗi ngăn chặn thay đổi.</t>
         </is>
       </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G99" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4414,9 +4444,9 @@
           <t>Xóa thông tin phiên đăng nhập ở local và chuyển hướng người dùng về trang chủ.</t>
         </is>
       </c>
-      <c r="G100" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G100" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4452,9 +4482,9 @@
           <t>Tải danh sách thông báo gửi riêng cho tài khoản Tenant hiển thị đầy đủ.</t>
         </is>
       </c>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4490,9 +4520,9 @@
           <t>Hiệu ứng chuyển đổi menu hiển thị mượt mà trên trình duyệt.</t>
         </is>
       </c>
-      <c r="G102" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G102" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4528,9 +4558,9 @@
           <t>Chuyển tab nhanh chóng và indicator di chuyển mượt mà trên di động.</t>
         </is>
       </c>
-      <c r="G103" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4566,9 +4596,9 @@
           <t>Hiệu ứng trượt ngang hoạt động mượt mà mang lại cảm giác mượt mà.</t>
         </is>
       </c>
-      <c r="G104" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G104" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4604,9 +4634,9 @@
           <t>Layout hiển thị chuẩn hai cột, cân đối không bị vỡ bố cục.</t>
         </is>
       </c>
-      <c r="G105" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4642,9 +4672,9 @@
           <t>Giao diện tự động co dãn sang chế độ di động, tối ưu diện tích hiển thị.</t>
         </is>
       </c>
-      <c r="G106" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G106" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4680,9 +4710,9 @@
           <t>Sidebar thu gọn thành dạng mini-icon, nội dung tự căn chỉnh vừa vặn.</t>
         </is>
       </c>
-      <c r="G107" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4718,9 +4748,9 @@
           <t>Dropdown bám đúng vị trí và đóng lại hợp lý khi người dùng scroll.</t>
         </is>
       </c>
-      <c r="G108" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G108" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4756,9 +4786,9 @@
           <t>Drawer menu hoạt động đúng hành vi, chuyển động trượt mượt mà.</t>
         </is>
       </c>
-      <c r="G109" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G109" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4794,9 +4824,9 @@
           <t>Cửa sổ chat mở rộng mượt mà, hiển thị lời chào và trạng thái hoạt động.</t>
         </is>
       </c>
-      <c r="G110" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G110" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4832,9 +4862,9 @@
           <t>Chatbot AI phản hồi chính xác giá phòng đơn chi nhánh Quận 1 từ dữ liệu DB thật.</t>
         </is>
       </c>
-      <c r="G111" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4870,9 +4900,9 @@
           <t>Hệ thống chặn gửi tin nhắn trống, nút gửi bị disabled.</t>
         </is>
       </c>
-      <c r="G112" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G112" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4908,9 +4938,9 @@
           <t>Giao diện hiển thị trang báo lỗi 404 thiết kế đẹp mắt với nút quay lại trang chủ.</t>
         </is>
       </c>
-      <c r="G113" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4946,9 +4976,9 @@
           <t>Spinner loading hiển thị mượt mà trước khi nạp xong component trang mới.</t>
         </is>
       </c>
-      <c r="G114" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G114" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -4984,9 +5014,9 @@
           <t>Hệ thống tự động đăng xuất tài khoản và đưa người dùng về /login kèm cảnh báo phiên hết hạn.</t>
         </is>
       </c>
-      <c r="G115" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -5023,9 +5053,9 @@
           <t>Chuyển hướng thành công sang giao diện yêu cầu OTP quên mật khẩu.</t>
         </is>
       </c>
-      <c r="G116" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G116" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -5062,9 +5092,9 @@
           <t>Chuyển hướng thành công sang giao diện đăng ký tài khoản mới.</t>
         </is>
       </c>
-      <c r="G117" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -5101,9 +5131,9 @@
           <t>Chuyển hướng thành công về trang đăng nhập hệ thống.</t>
         </is>
       </c>
-      <c r="G118" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G118" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -5140,9 +5170,9 @@
           <t>Hiệu ứng chuyển động GSAP trượt nền hoạt động trơn tru không giật lag.</t>
         </is>
       </c>
-      <c r="G119" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -5179,9 +5209,9 @@
           <t>Thẻ card xoay nhẹ 3D theo tọa độ chuột vô cùng đẹp mắt.</t>
         </is>
       </c>
-      <c r="G120" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G120" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -5218,9 +5248,9 @@
           <t>Hiệu ứng reveal cuộn trang hiển thị mượt mà bằng GSAP ScrollTrigger.</t>
         </is>
       </c>
-      <c r="G121" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -5257,9 +5287,9 @@
           <t>Khung đăng ký xuất hiện sinh động với hiệu ứng phóng to nhẹ scale: 1.05.</t>
         </is>
       </c>
-      <c r="G122" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G122" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -5296,9 +5326,9 @@
           <t>Transition chuyển đổi danh sách hoạt động êm ái, mang lại trải nghiệm người dùng cao cấp.</t>
         </is>
       </c>
-      <c r="G123" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G123" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -5334,9 +5364,9 @@
           <t>Hệ thống bắt lỗi kết nối an toàn, hiển thị giao diện báo lỗi thân thiện.</t>
         </is>
       </c>
-      <c r="G124" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G124" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -5372,9 +5402,9 @@
           <t>Hệ thống tự động lọc phòng trống làm mặc định, hiển thị kết quả chính xác.</t>
         </is>
       </c>
-      <c r="G125" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
@@ -5411,9 +5441,9 @@
           <t>Hệ thống kích hoạt tài khoản thành active sau khi xác thực OTP chính xác từ email.</t>
         </is>
       </c>
-      <c r="G126" s="9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
+      <c r="G126" s="11" t="inlineStr">
+        <is>
+          <t>SKIPPED</t>
         </is>
       </c>
     </row>
